--- a/outputs/daily/hr_rankings_2026-10-27_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-27_remaining.xlsx
@@ -755,12 +755,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -768,23 +768,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,30 +786,30 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>96.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -841,18 +829,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -889,7 +881,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -962,46 +954,14 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1035,12 +995,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1048,23 +1008,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>57.3</v>
+        <v>53.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,30 +1026,30 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>59.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R3" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U3" t="n">
         <v>16.6</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1121,18 +1069,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1169,7 +1121,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1242,46 +1194,14 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1295,56 +1215,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>55.9</v>
+        <v>51.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,30 +1266,30 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1391,7 +1299,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1401,18 +1309,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1429,12 +1341,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1444,12 +1356,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1459,109 +1371,77 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1575,56 +1455,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,30 +1506,30 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50.1</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R5" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>63.3</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1671,7 +1539,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1681,18 +1549,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1709,12 +1581,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1724,12 +1596,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1739,109 +1611,77 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1855,12 +1695,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1875,36 +1715,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>50.3</v>
+        <v>47</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,30 +1746,30 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>37.8</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1951,7 +1779,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1961,18 +1789,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1989,27 +1821,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2019,12 +1851,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -2034,94 +1866,62 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2135,56 +1935,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>50.2</v>
+        <v>46.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,30 +1986,30 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.2</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R7" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>25.3</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -2231,7 +2019,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2241,18 +2029,22 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2269,27 +2061,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2299,109 +2091,77 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2415,56 +2175,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>49.2</v>
+        <v>46.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,30 +2226,30 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R8" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>20.9</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2511,7 +2259,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2521,18 +2269,22 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2549,27 +2301,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2579,109 +2331,77 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2695,12 +2415,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2715,36 +2435,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>48.3</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,30 +2466,30 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>39.5</v>
+        <v>36.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R9" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>94.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>65.2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2791,7 +2499,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2801,18 +2509,22 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2829,27 +2541,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2859,12 +2571,12 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -2874,94 +2586,62 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2995,12 +2675,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3008,23 +2688,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>46.4</v>
+        <v>42.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3038,30 +2706,30 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>47.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U10" t="n">
         <v>13.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -3081,18 +2749,22 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3129,7 +2801,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3202,46 +2874,14 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3275,12 +2915,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3288,23 +2928,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,30 +2946,30 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>64.3</v>
+        <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -3361,18 +2989,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3409,7 +3041,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3482,46 +3114,14 @@
           <t>0.1288</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3535,12 +3135,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3555,36 +3155,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>41.1</v>
+        <v>37.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,30 +3186,30 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>94.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3631,7 +3219,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3641,18 +3229,22 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3669,27 +3261,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3699,109 +3291,77 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3815,12 +3375,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3835,36 +3395,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>40.7</v>
+        <v>35.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,30 +3426,30 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>86.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3911,7 +3459,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3921,18 +3469,22 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3949,27 +3501,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3979,109 +3531,77 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4095,56 +3615,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>37.7</v>
+        <v>32.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4158,30 +3666,30 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R14" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>52.4</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -4191,7 +3699,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4201,18 +3709,22 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4229,12 +3741,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4244,12 +3756,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4259,109 +3771,77 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4375,56 +3855,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>36.1</v>
+        <v>32.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,30 +3906,30 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>76.2</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -4471,7 +3939,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4481,18 +3949,22 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4509,12 +3981,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4524,12 +3996,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4539,109 +4011,77 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4655,32 +4095,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4688,23 +4128,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>35.8</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,30 +4146,30 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -4761,18 +4189,22 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4789,12 +4221,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4804,12 +4236,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4819,109 +4251,77 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4935,56 +4335,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>33.9</v>
+        <v>30.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,30 +4386,30 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>44.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -5031,7 +4419,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5041,18 +4429,22 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5069,12 +4461,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5084,12 +4476,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5099,109 +4491,77 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5215,12 +4575,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5235,36 +4595,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>33.8</v>
+        <v>29.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,30 +4626,30 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R18" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -5311,7 +4659,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5321,18 +4669,22 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5349,12 +4701,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5364,12 +4716,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5379,109 +4731,77 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1042</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5515,12 +4835,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5528,23 +4848,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>32.9</v>
+        <v>29.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5558,20 +4866,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.4</v>
+        <v>40.2</v>
       </c>
       <c r="R19" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5581,7 +4889,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -5601,18 +4909,22 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5649,7 +4961,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5722,46 +5034,14 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6121,12 +5401,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6134,23 +5414,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>57.4</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6164,30 +5432,30 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>96.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -6207,18 +5475,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -6255,7 +5527,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -6328,46 +5600,14 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6401,12 +5641,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6414,23 +5654,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>57.3</v>
+        <v>53.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6444,30 +5672,30 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>59.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R3" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U3" t="n">
         <v>16.6</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -6487,18 +5715,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6535,7 +5767,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -6608,46 +5840,14 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6661,56 +5861,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>55.9</v>
+        <v>51.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6724,30 +5912,30 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -6757,7 +5945,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6767,18 +5955,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6795,12 +5987,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6810,12 +6002,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6825,109 +6017,77 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6941,56 +6101,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7004,30 +6152,30 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>50.1</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R5" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>63.3</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -7037,7 +6185,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -7047,18 +6195,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -7075,12 +6227,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7090,12 +6242,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7105,109 +6257,77 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7221,12 +6341,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7241,36 +6361,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>50.3</v>
+        <v>47</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,30 +6392,30 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>37.8</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -7317,7 +6425,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7327,18 +6435,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -7355,27 +6467,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7385,12 +6497,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -7400,94 +6512,62 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7501,56 +6581,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>50.2</v>
+        <v>46.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7564,30 +6632,30 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.2</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R7" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>25.3</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -7597,7 +6665,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7607,18 +6675,22 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7635,27 +6707,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7665,109 +6737,77 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7781,56 +6821,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>49.2</v>
+        <v>46.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7844,30 +6872,30 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R8" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>20.9</v>
+        <v>25.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -7877,7 +6905,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7887,18 +6915,22 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7915,27 +6947,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7945,109 +6977,77 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8061,12 +7061,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8081,36 +7081,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>48.3</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8124,30 +7112,30 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>39.5</v>
+        <v>36.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R9" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>94.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>65.2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -8157,7 +7145,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8167,18 +7155,22 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8195,27 +7187,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8225,12 +7217,12 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
@@ -8240,94 +7232,62 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8361,12 +7321,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8374,23 +7334,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>46.4</v>
+        <v>42.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8404,30 +7352,30 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>47.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U10" t="n">
         <v>13.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -8447,18 +7395,22 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8495,7 +7447,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8568,46 +7520,14 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8641,12 +7561,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8654,23 +7574,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8684,30 +7592,30 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>64.3</v>
+        <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -8727,18 +7635,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8775,7 +7687,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8848,46 +7760,14 @@
           <t>0.1288</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8901,12 +7781,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8921,36 +7801,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>41.1</v>
+        <v>37.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8964,30 +7832,30 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>94.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -8997,7 +7865,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -9007,18 +7875,22 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -9035,27 +7907,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9065,109 +7937,77 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9181,12 +8021,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9201,36 +8041,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>40.7</v>
+        <v>35.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9244,30 +8072,30 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>86.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -9277,7 +8105,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9287,18 +8115,22 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -9315,27 +8147,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9345,109 +8177,77 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9461,56 +8261,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>37.7</v>
+        <v>32.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9524,30 +8312,30 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R14" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>52.4</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -9557,7 +8345,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9567,18 +8355,22 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9595,12 +8387,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -9610,12 +8402,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9625,109 +8417,77 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9741,56 +8501,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>36.1</v>
+        <v>32.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9804,30 +8552,30 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>76.2</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -9837,7 +8585,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9847,18 +8595,22 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9875,12 +8627,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9890,12 +8642,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9905,109 +8657,77 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10021,32 +8741,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10054,23 +8774,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>35.8</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10084,30 +8792,30 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.2</v>
+        <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -10127,18 +8835,22 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10155,12 +8867,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10170,12 +8882,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10185,109 +8897,77 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10301,56 +8981,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>33.9</v>
+        <v>30.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10364,30 +9032,30 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>44.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -10397,7 +9065,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -10407,18 +9075,22 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10435,12 +9107,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10450,12 +9122,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10465,109 +9137,77 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10581,12 +9221,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10601,36 +9241,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>33.8</v>
+        <v>29.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10644,30 +9272,30 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R18" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -10677,7 +9305,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10687,18 +9315,22 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10715,12 +9347,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10730,12 +9362,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10745,109 +9377,77 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>0.1042</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10881,12 +9481,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-28T00:00:00Z</t>
+          <t>2026-10-29T00:00:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10894,23 +9494,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>32.9</v>
+        <v>29.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10924,20 +9512,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.4</v>
+        <v>40.2</v>
       </c>
       <c r="R19" t="n">
-        <v>40.1</v>
+        <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10947,7 +9535,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -10967,18 +9555,22 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -11015,7 +9607,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11088,46 +9680,14 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0.1595</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
